--- a/public/templates/examples/A-031-GovernanceReportingCalendar-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-031-GovernanceReportingCalendar-EXAMPLE-L.xlsx
@@ -214,7 +214,7 @@
     <t xml:space="preserve">NIST SP 800-53 Rev. 5: CA-7, PM-6, PM-9</t>
   </si>
   <si>
-    <t xml:space="preserve">Indiana statutes and administrative code: HEA 1169 (2021) — Cyber Incident Reporting to IOT (designate and update the primary reporting contact before September 1)</t>
+    <t xml:space="preserve">Indiana statutes and administrative code: HEA 1169 (2021): Cyber Incident Reporting to IOT (designate and update the primary reporting contact before September 1)</t>
   </si>
   <si>
     <t xml:space="preserve">Approval Signatures</t>
@@ -276,17 +276,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="0"/>
     </font>
     <font>

--- a/public/templates/examples/A-031-GovernanceReportingCalendar-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-031-GovernanceReportingCalendar-EXAMPLE-L.xlsx
@@ -270,7 +270,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -517,19 +517,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>552240</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>552240</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="857250" cy="857250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -554,7 +549,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -677,12 +672,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/examples/A-031-GovernanceReportingCalendar-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-031-GovernanceReportingCalendar-EXAMPLE-L.xlsx
@@ -5,12 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="80">
   <si>
     <t xml:space="preserve">Tri-River Regional 911 Center   ·   Worked Example</t>
   </si>
@@ -187,7 +187,7 @@
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Summary</t>
+    <t>Summary (as of 2026-06-02)</t>
   </si>
   <si>
     <t xml:space="preserve">Items tracked</t>
@@ -257,14 +257,18 @@
   </si>
   <si>
     <t xml:space="preserve">Initial issue</t>
+  </si>
+  <si>
+    <t>Overdue</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -390,7 +394,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -440,6 +444,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -939,11 +951,11 @@
       <c r="D11" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>22</v>
+      <c r="E11" s="13">
+        <v>46114</v>
+      </c>
+      <c r="F11" s="13">
+        <v>46205</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>23</v>
@@ -962,11 +974,11 @@
       <c r="D12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>27</v>
+      <c r="E12" s="13">
+        <v>46122</v>
+      </c>
+      <c r="F12" s="13">
+        <v>46213</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>23</v>
@@ -985,14 +997,14 @@
       <c r="D13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>32</v>
+      <c r="E13" s="13">
+        <v>46143</v>
+      </c>
+      <c r="F13" s="13">
+        <v>46174</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1008,11 +1020,11 @@
       <c r="D14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>37</v>
+      <c r="E14" s="13">
+        <v>46037</v>
+      </c>
+      <c r="F14" s="13">
+        <v>46402</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>23</v>
@@ -1031,11 +1043,11 @@
       <c r="D15" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>40</v>
+      <c r="E15" s="13">
+        <v>46147</v>
+      </c>
+      <c r="F15" s="13">
+        <v>46178</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>23</v>
@@ -1054,11 +1066,11 @@
       <c r="D16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>44</v>
+      <c r="E16" s="13">
+        <v>46145</v>
+      </c>
+      <c r="F16" s="13">
+        <v>46176</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>23</v>
@@ -1077,11 +1089,11 @@
       <c r="D17" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>50</v>
+      <c r="E17" s="13">
+        <v>45894</v>
+      </c>
+      <c r="F17" s="13">
+        <v>46259</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>23</v>
@@ -1100,11 +1112,11 @@
       <c r="D18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>54</v>
+      <c r="E18" s="13">
+        <v>46120</v>
+      </c>
+      <c r="F18" s="13">
+        <v>46211</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>23</v>
@@ -1127,7 +1139,6 @@
       </c>
       <c r="C21" s="8" t="n">
         <f aca="false">COUNTA(A11:A18)</f>
-        <v>8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1136,7 +1147,6 @@
       </c>
       <c r="C22" s="8" t="n">
         <f aca="false">COUNTIF(G11:G18,"Overdue")</f>
-        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1144,8 +1154,7 @@
         <v>58</v>
       </c>
       <c r="C23" s="8" t="n">
-        <f aca="true">COUNTIF(F11:F18,"&lt;"&amp;TODAY())</f>
-        <v>0</v>
+        <f aca="true">COUNTIF(F11:F18,"&lt;"&amp;DATE(2026,6,2))</f>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1249,8 +1258,8 @@
       <c r="C35" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>71</v>
+      <c r="D35" s="14">
+        <v>46042</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1263,8 +1272,8 @@
       <c r="C36" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>71</v>
+      <c r="D36" s="14">
+        <v>46042</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1296,8 +1305,8 @@
       <c r="A40" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>71</v>
+      <c r="B40" s="14">
+        <v>46042</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>5</v>
@@ -1331,7 +1340,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
